--- a/data/bloomberg/corn_iv.xlsx
+++ b/data/bloomberg/corn_iv.xlsx
@@ -7278,7 +7278,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{267EB9AF-8289-4B46-8FE4-AC3DF1747803}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{345FA08B-B40E-4C6D-B560-20CE1659D160}">
   <ds:schemaRefs/>
 </ds:datastoreItem>
 </file>